--- a/src/product/data/FundingSource_Field_Values.xlsx
+++ b/src/product/data/FundingSource_Field_Values.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MergeOrg2_Proj\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jenkins_Playwright_FW\govgrants-playwright-automation\src\product\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9372832-2718-4735-9356-940A77BAFD58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEF8FBAB-1619-4D36-B502-A8C87CE60977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{11C5240F-7765-4FC9-A357-1384C2AAB3E6}"/>
   </bookViews>
@@ -103,10 +103,10 @@
     <t>CostCategory__c</t>
   </si>
   <si>
-    <t>Contractual</t>
-  </si>
-  <si>
     <t>Type__c</t>
+  </si>
+  <si>
+    <t>Contractual: Contracts</t>
   </si>
 </sst>
 </file>
@@ -743,7 +743,7 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -799,7 +799,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>15</v>
